--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T10:02:10-03:00</t>
+    <t>2026-09-25T17:16:20-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-25T17:16:20-03:00</t>
+    <t>2026-09-28T11:57:19-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T11:57:19-03:00</t>
+    <t>2026-09-30T19:22:44-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="254">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T19:22:44-03:00</t>
+    <t>2026-10-08T21:08:49-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -702,7 +702,7 @@
 </t>
   </si>
   <si>
-    <t>open</t>
+    <t>closed</t>
   </si>
   <si>
     <t>.player</t>
@@ -725,6 +725,12 @@
   </si>
   <si>
     <t>The actual ingredient - either a substance (simple ingredient) or another medication of a medication.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.item[x]:itemCodeableConcept</t>
+  </si>
+  <si>
+    <t>itemCodeableConcept</t>
   </si>
   <si>
     <t>Medication.ingredient.isActive</t>
@@ -1110,12 +1116,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN30"/>
+  <dimension ref="A1:AN31"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.75" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.96875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="34.52734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="19.109375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="35.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.65234375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.265625" customWidth="true" bestFit="true"/>
@@ -3663,9 +3669,11 @@
         <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>226</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>77</v>
       </c>
@@ -3686,17 +3694,17 @@
         <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>226</v>
+        <v>148</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -3745,10 +3753,10 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="AH23" t="s" s="2">
         <v>87</v>
@@ -3760,24 +3768,24 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3800,16 +3808,18 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>231</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
@@ -3857,7 +3867,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -3872,24 +3882,24 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>187</v>
+        <v>232</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>234</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3912,13 +3922,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3969,7 +3979,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -3984,24 +3994,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>170</v>
+        <v>235</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4024,13 +4034,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>195</v>
+        <v>238</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>196</v>
+        <v>239</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4081,7 +4091,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>197</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4093,13 +4103,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>170</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>198</v>
+        <v>240</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4110,21 +4120,21 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>200</v>
+        <v>77</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4136,17 +4146,15 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>132</v>
+        <v>194</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>196</v>
+      </c>
+      <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4195,19 +4203,19 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4224,14 +4232,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4244,26 +4252,24 @@
         <v>77</v>
       </c>
       <c r="I28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="O28" t="s" s="2">
-        <v>209</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
@@ -4311,7 +4317,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4329,7 +4335,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>130</v>
+        <v>198</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4340,42 +4346,46 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>208</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4423,39 +4433,39 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>170</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>245</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4478,13 +4488,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>247</v>
+        <v>194</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4535,7 +4545,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4553,13 +4563,125 @@
         <v>170</v>
       </c>
       <c r="AL30" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN30" t="s" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L31" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN30" t="s" s="2">
+      <c r="M31" t="s" s="2">
         <v>251</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK31" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>253</v>
       </c>
     </row>
   </sheetData>

--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T21:08:49-03:00</t>
+    <t>2026-10-16T11:47:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/output/StructureDefinition-br-core-medication.xlsx
+++ b/output/StructureDefinition-br-core-medication.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T11:47:57-03:00</t>
+    <t>2026-10-19T17:00:57-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
